--- a/artfynd/A 9166-2023 artfynd.xlsx
+++ b/artfynd/A 9166-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY52"/>
+  <dimension ref="A1:AY49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115891546</v>
+        <v>115891640</v>
       </c>
       <c r="B2" t="n">
-        <v>94059</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2809</v>
+        <v>306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>532878</v>
+        <v>532325</v>
       </c>
       <c r="R2" t="n">
-        <v>7235054</v>
+        <v>7234926</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -764,7 +759,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>7869</t>
+          <t>7152</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -775,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Josefina Pehrson</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -786,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115891724</v>
+        <v>115891580</v>
       </c>
       <c r="B3" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532736</v>
+        <v>532924</v>
       </c>
       <c r="R3" t="n">
-        <v>7234829</v>
+        <v>7235009</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -875,7 +865,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>7451</t>
+          <t>7444</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -897,54 +887,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115891454</v>
+        <v>115891619</v>
       </c>
       <c r="B4" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>532921</v>
+        <v>532296</v>
       </c>
       <c r="R4" t="n">
-        <v>7235155</v>
+        <v>7234963</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -979,11 +960,6 @@
           <t>2023-09-15</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>stöttes</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -995,7 +971,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>7295</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1006,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Josefina Pehrson</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1017,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115891101</v>
+        <v>115891063</v>
       </c>
       <c r="B5" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1033,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1057,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>533141</v>
+        <v>533158</v>
       </c>
       <c r="R5" t="n">
-        <v>7235339</v>
+        <v>7235358</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,24 +1075,9 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>7227</t>
+          <t>7206</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1143,15 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115891723</v>
+        <v>115891366</v>
       </c>
       <c r="B6" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>532739</v>
+        <v>533033</v>
       </c>
       <c r="R6" t="n">
-        <v>7234830</v>
+        <v>7235206</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1232,7 +1183,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>7452</t>
+          <t>7286</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1254,15 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115891580</v>
+        <v>115891573</v>
       </c>
       <c r="B7" t="n">
-        <v>86661</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1294,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>532924</v>
+        <v>532935</v>
       </c>
       <c r="R7" t="n">
-        <v>7235009</v>
+        <v>7235020</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1343,7 +1289,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>7444</t>
+          <t>7865</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1365,15 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115891612</v>
+        <v>115891642</v>
       </c>
       <c r="B8" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1381,21 +1322,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1405,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>532897</v>
+        <v>532302</v>
       </c>
       <c r="R8" t="n">
-        <v>7234979</v>
+        <v>7234924</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1454,7 +1395,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>7435</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1465,7 +1406,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Josefina Pehrson</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1476,15 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115891674</v>
+        <v>115891442</v>
       </c>
       <c r="B9" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1492,21 +1428,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1516,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>532624</v>
+        <v>532956</v>
       </c>
       <c r="R9" t="n">
-        <v>7234881</v>
+        <v>7235163</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1565,7 +1501,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>7289</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1590,12 +1526,7 @@
         <v>115891561</v>
       </c>
       <c r="B10" t="n">
-        <v>90328</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1698,37 +1629,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115891120</v>
+        <v>115891588</v>
       </c>
       <c r="B11" t="n">
-        <v>91263</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4769</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1738,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>533195</v>
+        <v>532776</v>
       </c>
       <c r="R11" t="n">
-        <v>7235331</v>
+        <v>7235004</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1787,7 +1713,7 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>7177</t>
+          <t>7378</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1809,37 +1735,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115891677</v>
+        <v>115891648</v>
       </c>
       <c r="B12" t="n">
-        <v>79587</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1849,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>532668</v>
+        <v>532301</v>
       </c>
       <c r="R12" t="n">
-        <v>7234868</v>
+        <v>7234915</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1898,7 +1819,7 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>7458</t>
+          <t>7170</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1909,7 +1830,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Josefina Pehrson</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1920,37 +1841,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115891449</v>
+        <v>115891641</v>
       </c>
       <c r="B13" t="n">
-        <v>79593</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>1467</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1960,10 +1876,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>532912</v>
+        <v>532334</v>
       </c>
       <c r="R13" t="n">
-        <v>7235157</v>
+        <v>7234925</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2009,7 +1925,7 @@
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>7299</t>
+          <t>7135</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2020,7 +1936,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Josefina Pehrson</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2031,37 +1947,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>115891675</v>
+        <v>115891634</v>
       </c>
       <c r="B14" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92292</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>1506</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2071,10 +1982,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>532626</v>
+        <v>532307</v>
       </c>
       <c r="R14" t="n">
-        <v>7234880</v>
+        <v>7234938</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2120,7 +2031,7 @@
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>7463</t>
+          <t>7171</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2131,7 +2042,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Josefina Pehrson</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2142,37 +2053,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>115891600</v>
+        <v>115891586</v>
       </c>
       <c r="B15" t="n">
-        <v>104722</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97453</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221725</v>
+        <v>1841</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2182,10 +2088,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>532748</v>
+        <v>532854</v>
       </c>
       <c r="R15" t="n">
-        <v>7234995</v>
+        <v>7235007</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2231,7 +2137,7 @@
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>7384</t>
+          <t>7332</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2253,37 +2159,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>115891556</v>
+        <v>115891447</v>
       </c>
       <c r="B16" t="n">
-        <v>91023</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3298</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2293,10 +2194,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>532839</v>
+        <v>532933</v>
       </c>
       <c r="R16" t="n">
-        <v>7235036</v>
+        <v>7235159</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2342,7 +2243,7 @@
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>7339</t>
+          <t>7291</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2364,15 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>115891157</v>
+        <v>115891470</v>
       </c>
       <c r="B17" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2380,39 +2276,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>533207</v>
+        <v>532900</v>
       </c>
       <c r="R17" t="n">
-        <v>7235314</v>
+        <v>7235146</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2447,11 +2338,6 @@
           <t>2023-09-15</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Hackmärken färska</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2463,7 +2349,7 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>7179</t>
+          <t>7300</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2485,15 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>115891007</v>
+        <v>115891579</v>
       </c>
       <c r="B18" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2501,21 +2382,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2525,10 +2406,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>533169</v>
+        <v>532929</v>
       </c>
       <c r="R18" t="n">
-        <v>7235388</v>
+        <v>7235009</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2574,7 +2455,7 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>7218</t>
+          <t>7863</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2596,15 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115891442</v>
+        <v>115891659</v>
       </c>
       <c r="B19" t="n">
-        <v>90328</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2612,21 +2488,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2636,10 +2512,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>532956</v>
+        <v>532734</v>
       </c>
       <c r="R19" t="n">
-        <v>7235163</v>
+        <v>7234896</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2685,7 +2561,7 @@
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>7289</t>
+          <t>7404</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2707,15 +2583,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>115891625</v>
+        <v>115891674</v>
       </c>
       <c r="B20" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2723,21 +2594,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2747,10 +2618,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>532724</v>
+        <v>532624</v>
       </c>
       <c r="R20" t="n">
-        <v>7234945</v>
+        <v>7234881</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2796,7 +2667,7 @@
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>7393</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2818,15 +2689,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>115891619</v>
+        <v>115891724</v>
       </c>
       <c r="B21" t="n">
-        <v>86661</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2834,21 +2700,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>510</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2858,10 +2724,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>532296</v>
+        <v>532736</v>
       </c>
       <c r="R21" t="n">
-        <v>7234963</v>
+        <v>7234829</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2907,7 +2773,7 @@
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>7451</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2918,7 +2784,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Josefina Pehrson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2929,15 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>115891455</v>
+        <v>115891105</v>
       </c>
       <c r="B22" t="n">
-        <v>79587</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96603</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2945,21 +2806,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>2166</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skör kvastmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dicranum fragilifolium</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Lindb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2969,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>532914</v>
+        <v>533142</v>
       </c>
       <c r="R22" t="n">
-        <v>7235155</v>
+        <v>7235337</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3018,7 +2879,7 @@
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>7297</t>
+          <t>7226</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3040,37 +2901,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>115891659</v>
+        <v>115891546</v>
       </c>
       <c r="B23" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>2809</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3080,10 +2936,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>532734</v>
+        <v>532878</v>
       </c>
       <c r="R23" t="n">
-        <v>7234896</v>
+        <v>7235054</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3129,7 +2985,7 @@
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>7404</t>
+          <t>7869</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3151,37 +3007,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115891572</v>
+        <v>115891145</v>
       </c>
       <c r="B24" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3191,10 +3042,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>532776</v>
+        <v>533205</v>
       </c>
       <c r="R24" t="n">
-        <v>7235022</v>
+        <v>7235317</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3240,7 +3091,7 @@
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>7347</t>
+          <t>7178</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3262,15 +3113,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>115891575</v>
+        <v>115891556</v>
       </c>
       <c r="B25" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3278,21 +3124,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3302,10 +3148,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>532935</v>
+        <v>532839</v>
       </c>
       <c r="R25" t="n">
-        <v>7235019</v>
+        <v>7235036</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3351,7 +3197,7 @@
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>7866</t>
+          <t>7339</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3373,37 +3219,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>115891579</v>
+        <v>115891566</v>
       </c>
       <c r="B26" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3413,10 +3254,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>532929</v>
+        <v>532949</v>
       </c>
       <c r="R26" t="n">
-        <v>7235009</v>
+        <v>7235027</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3462,7 +3303,7 @@
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>7863</t>
+          <t>7331</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3484,37 +3325,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>115891447</v>
+        <v>115891120</v>
       </c>
       <c r="B27" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>4769</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3524,10 +3360,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>532933</v>
+        <v>533195</v>
       </c>
       <c r="R27" t="n">
-        <v>7235159</v>
+        <v>7235331</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3573,7 +3409,7 @@
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>7291</t>
+          <t>7177</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3595,15 +3431,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>115891522</v>
+        <v>115891539</v>
       </c>
       <c r="B28" t="n">
-        <v>79518</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3611,21 +3442,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229497</v>
+        <v>4769</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3635,10 +3466,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>532898</v>
+        <v>532861</v>
       </c>
       <c r="R28" t="n">
-        <v>7235091</v>
+        <v>7235064</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3684,7 +3515,7 @@
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>7310</t>
+          <t>7871</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3706,37 +3537,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>115891470</v>
+        <v>115891575</v>
       </c>
       <c r="B29" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3746,10 +3572,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>532900</v>
+        <v>532935</v>
       </c>
       <c r="R29" t="n">
-        <v>7235146</v>
+        <v>7235019</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3795,7 +3621,7 @@
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>7300</t>
+          <t>7866</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3817,37 +3643,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>115891588</v>
+        <v>115891646</v>
       </c>
       <c r="B30" t="n">
-        <v>90346</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3857,10 +3678,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>532776</v>
+        <v>532796</v>
       </c>
       <c r="R30" t="n">
-        <v>7235004</v>
+        <v>7234917</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3906,7 +3727,7 @@
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>7378</t>
+          <t>7417</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3928,37 +3749,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>115891539</v>
+        <v>115890963</v>
       </c>
       <c r="B31" t="n">
-        <v>91263</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4769</v>
+        <v>6437</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3968,10 +3784,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>532861</v>
+        <v>533262</v>
       </c>
       <c r="R31" t="n">
-        <v>7235064</v>
+        <v>7235415</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4017,7 +3833,7 @@
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>7871</t>
+          <t>7142</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4039,15 +3855,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>115891697</v>
+        <v>115942687</v>
       </c>
       <c r="B32" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4055,21 +3866,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6437</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4079,10 +3890,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>532739</v>
+        <v>533375</v>
       </c>
       <c r="R32" t="n">
-        <v>7234848</v>
+        <v>7235480</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4128,7 +3939,7 @@
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>7453</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4150,37 +3961,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>115891488</v>
+        <v>115891675</v>
       </c>
       <c r="B33" t="n">
-        <v>79518</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4190,10 +3996,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>532905</v>
+        <v>532626</v>
       </c>
       <c r="R33" t="n">
-        <v>7235130</v>
+        <v>7234880</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4239,7 +4045,7 @@
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>7305</t>
+          <t>7463</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4261,15 +4067,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>115890963</v>
+        <v>115891697</v>
       </c>
       <c r="B34" t="n">
-        <v>77895</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4277,21 +4078,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6437</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4301,10 +4102,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>533262</v>
+        <v>532739</v>
       </c>
       <c r="R34" t="n">
-        <v>7235415</v>
+        <v>7234848</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4350,7 +4151,7 @@
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>7142</t>
+          <t>7453</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4372,37 +4173,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>115891640</v>
+        <v>115891723</v>
       </c>
       <c r="B35" t="n">
-        <v>74634</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>306</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4412,10 +4208,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>532325</v>
+        <v>532739</v>
       </c>
       <c r="R35" t="n">
-        <v>7234926</v>
+        <v>7234830</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4461,7 +4257,7 @@
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>7152</t>
+          <t>7452</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4472,7 +4268,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Josefina Pehrson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4483,37 +4279,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>115891063</v>
+        <v>115891455</v>
       </c>
       <c r="B36" t="n">
-        <v>90615</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4523,10 +4314,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>533158</v>
+        <v>532914</v>
       </c>
       <c r="R36" t="n">
-        <v>7235358</v>
+        <v>7235155</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4572,7 +4363,7 @@
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>7206</t>
+          <t>7297</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4594,37 +4385,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>115891641</v>
+        <v>115891677</v>
       </c>
       <c r="B37" t="n">
-        <v>74652</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1467</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4634,10 +4420,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>532334</v>
+        <v>532668</v>
       </c>
       <c r="R37" t="n">
-        <v>7234925</v>
+        <v>7234868</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4683,7 +4469,7 @@
       </c>
       <c r="AR37" t="inlineStr">
         <is>
-          <t>7135</t>
+          <t>7458</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4694,7 +4480,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Josefina Pehrson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4705,15 +4491,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>115891105</v>
+        <v>115891449</v>
       </c>
       <c r="B38" t="n">
-        <v>94324</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4721,21 +4502,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2166</v>
+        <v>6463</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skör kvastmossa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dicranum fragilifolium</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Lindb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4745,10 +4526,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>533142</v>
+        <v>532912</v>
       </c>
       <c r="R38" t="n">
-        <v>7235337</v>
+        <v>7235157</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4794,7 +4575,7 @@
       </c>
       <c r="AR38" t="inlineStr">
         <is>
-          <t>7226</t>
+          <t>7299</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4816,37 +4597,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>115891366</v>
+        <v>115891678</v>
       </c>
       <c r="B39" t="n">
-        <v>90615</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>6463</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4856,10 +4632,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>533033</v>
+        <v>532668</v>
       </c>
       <c r="R39" t="n">
-        <v>7235206</v>
+        <v>7234868</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4905,7 +4681,7 @@
       </c>
       <c r="AR39" t="inlineStr">
         <is>
-          <t>7286</t>
+          <t>7459</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4927,15 +4703,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>115891573</v>
+        <v>115891157</v>
       </c>
       <c r="B40" t="n">
-        <v>90615</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4943,34 +4714,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>532935</v>
+        <v>533207</v>
       </c>
       <c r="R40" t="n">
-        <v>7235020</v>
+        <v>7235314</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5005,6 +4781,11 @@
           <t>2023-09-15</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Hackmärken färska</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5016,7 +4797,7 @@
       </c>
       <c r="AR40" t="inlineStr">
         <is>
-          <t>7865</t>
+          <t>7179</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5038,15 +4819,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>115891145</v>
+        <v>115891454</v>
       </c>
       <c r="B41" t="n">
-        <v>91023</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5054,34 +4830,38 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3298</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>533205</v>
+        <v>532921</v>
       </c>
       <c r="R41" t="n">
-        <v>7235317</v>
+        <v>7235155</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5116,6 +4896,11 @@
           <t>2023-09-15</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>stöttes</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5127,7 +4912,7 @@
       </c>
       <c r="AR41" t="inlineStr">
         <is>
-          <t>7178</t>
+          <t>7295</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5149,37 +4934,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>115891566</v>
+        <v>115891007</v>
       </c>
       <c r="B42" t="n">
-        <v>91023</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3298</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5189,10 +4969,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>532949</v>
+        <v>533169</v>
       </c>
       <c r="R42" t="n">
-        <v>7235027</v>
+        <v>7235388</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5238,7 +5018,7 @@
       </c>
       <c r="AR42" t="inlineStr">
         <is>
-          <t>7331</t>
+          <t>7218</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5260,15 +5040,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>115891350</v>
+        <v>115891738</v>
       </c>
       <c r="B43" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5276,21 +5051,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5300,10 +5075,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>533030</v>
+        <v>532774</v>
       </c>
       <c r="R43" t="n">
-        <v>7235216</v>
+        <v>7234807</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5349,7 +5124,7 @@
       </c>
       <c r="AR43" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>7448</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5371,37 +5146,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>115891102</v>
+        <v>115891600</v>
       </c>
       <c r="B44" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>221725</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5411,10 +5181,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>533198</v>
+        <v>532748</v>
       </c>
       <c r="R44" t="n">
-        <v>7235338</v>
+        <v>7234995</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5460,7 +5230,7 @@
       </c>
       <c r="AR44" t="inlineStr">
         <is>
-          <t>7167</t>
+          <t>7384</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5482,15 +5252,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>115891646</v>
+        <v>115942683</v>
       </c>
       <c r="B45" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105255</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5498,21 +5263,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>223985</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smal ängssyra</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rumex acetosa var. serpentinicola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Rune</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5522,10 +5287,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>532796</v>
+        <v>533337</v>
       </c>
       <c r="R45" t="n">
-        <v>7234917</v>
+        <v>7235490</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5571,7 +5336,7 @@
       </c>
       <c r="AR45" t="inlineStr">
         <is>
-          <t>7417</t>
+          <t>7475</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5593,37 +5358,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>115891678</v>
+        <v>115942680</v>
       </c>
       <c r="B46" t="n">
-        <v>79593</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105706</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6463</v>
+        <v>224078</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spenslig fjällnejlika</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Viscaria alpina var. serpentinicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Rune</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5633,10 +5393,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>532668</v>
+        <v>533339</v>
       </c>
       <c r="R46" t="n">
-        <v>7234867</v>
+        <v>7235494</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5682,7 +5442,7 @@
       </c>
       <c r="AR46" t="inlineStr">
         <is>
-          <t>7459</t>
+          <t>7474</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5704,37 +5464,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>115891586</v>
+        <v>115891488</v>
       </c>
       <c r="B47" t="n">
-        <v>95523</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1841</v>
+        <v>229497</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5744,10 +5499,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>532854</v>
+        <v>532905</v>
       </c>
       <c r="R47" t="n">
-        <v>7235007</v>
+        <v>7235130</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5793,7 +5548,7 @@
       </c>
       <c r="AR47" t="inlineStr">
         <is>
-          <t>7332</t>
+          <t>7305</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5815,37 +5570,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>115891634</v>
+        <v>115891522</v>
       </c>
       <c r="B48" t="n">
-        <v>90685</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1506</v>
+        <v>229497</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5855,10 +5605,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>532307</v>
+        <v>532898</v>
       </c>
       <c r="R48" t="n">
-        <v>7234938</v>
+        <v>7235091</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5904,7 +5654,7 @@
       </c>
       <c r="AR48" t="inlineStr">
         <is>
-          <t>7171</t>
+          <t>7310</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5915,7 +5665,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Josefina Pehrson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5926,15 +5676,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>115942680</v>
+        <v>115942686</v>
       </c>
       <c r="B49" t="n">
-        <v>104205</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5942,21 +5687,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>224078</v>
+        <v>229821</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spenslig fjällnejlika</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Viscaria alpina var. serpentinicola</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Rune</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5966,10 +5711,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>533339</v>
+        <v>533368</v>
       </c>
       <c r="R49" t="n">
-        <v>7235494</v>
+        <v>7235481</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6015,7 +5760,7 @@
       </c>
       <c r="AR49" t="inlineStr">
         <is>
-          <t>7474</t>
+          <t>7125</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6030,339 +5775,6 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr">
-        <is>
-          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>115942687</v>
-      </c>
-      <c r="B50" t="n">
-        <v>77895</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>6437</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Blanksvart spiklav</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Calicium denigratum</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>Dikanäs - Kittelfjäll, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q50" t="n">
-        <v>533375</v>
-      </c>
-      <c r="R50" t="n">
-        <v>7235480</v>
-      </c>
-      <c r="S50" t="n">
-        <v>5</v>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>2023-09-15</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>2023-09-15</t>
-        </is>
-      </c>
-      <c r="AD50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>7124</t>
-        </is>
-      </c>
-      <c r="AT50" t="inlineStr"/>
-      <c r="AW50" t="inlineStr">
-        <is>
-          <t>Rickard Gustafsson</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>Josefina Pehrson</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr">
-        <is>
-          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>115942683</v>
-      </c>
-      <c r="B51" t="n">
-        <v>103767</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>223985</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Smal ängssyra</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Rumex acetosa var. serpentinicola</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Rune</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Dikanäs - Kittelfjäll, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q51" t="n">
-        <v>533337</v>
-      </c>
-      <c r="R51" t="n">
-        <v>7235490</v>
-      </c>
-      <c r="S51" t="n">
-        <v>5</v>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>2023-09-15</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>2023-09-15</t>
-        </is>
-      </c>
-      <c r="AD51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>7475</t>
-        </is>
-      </c>
-      <c r="AT51" t="inlineStr"/>
-      <c r="AW51" t="inlineStr">
-        <is>
-          <t>Rickard Gustafsson</t>
-        </is>
-      </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>Josefina Pehrson</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr">
-        <is>
-          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>115942686</v>
-      </c>
-      <c r="B52" t="n">
-        <v>79074</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>229821</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Vedflamlav</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Ramboldia elabens</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>Dikanäs - Kittelfjäll, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q52" t="n">
-        <v>533368</v>
-      </c>
-      <c r="R52" t="n">
-        <v>7235481</v>
-      </c>
-      <c r="S52" t="n">
-        <v>5</v>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>2023-09-15</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>2023-09-15</t>
-        </is>
-      </c>
-      <c r="AD52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>7125</t>
-        </is>
-      </c>
-      <c r="AT52" t="inlineStr"/>
-      <c r="AW52" t="inlineStr">
-        <is>
-          <t>Rickard Gustafsson</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>Josefina Pehrson</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr">
         <is>
           <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
         </is>
